--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q4_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001932944880543333</v>
+        <v>0.001927615752503532</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001932944880543333</v>
+        <v>0.001927615752503532</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002233639717304078</v>
+        <v>0.002748762807471297</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001900219944308653</v>
+        <v>0.001897398207266988</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001900219944308653</v>
+        <v>0.001897398207266988</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002324913702181125</v>
+        <v>0.002882685112428571</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001903299642430837</v>
+        <v>0.001899406878793106</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001903299642430837</v>
+        <v>0.001899406878793106</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002233027157011018</v>
+        <v>0.002766349517223275</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001900454042660818</v>
+        <v>0.001893881995597052</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001900454042660818</v>
+        <v>0.001893881995597052</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002154110377145377</v>
+        <v>0.002653875175022493</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001885409818854197</v>
+        <v>0.00187533877123906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001885409818854197</v>
+        <v>0.00187533877123906</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002078377142822</v>
+        <v>0.00254144399944762</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001874040618348327</v>
+        <v>0.001860092832946043</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001874040618348327</v>
+        <v>0.001860092832946043</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001993666386063672</v>
+        <v>0.002419467876313378</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001852846280823052</v>
+        <v>0.001834717989877848</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001852846280823052</v>
+        <v>0.001834717989877848</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001905181113230773</v>
+        <v>0.002292450614504925</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001829604710351287</v>
+        <v>0.001807224034172523</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001829604710351287</v>
+        <v>0.001807224034172523</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001813335282013818</v>
+        <v>0.002162712788211426</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001804817416818885</v>
+        <v>0.00177829682478012</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001804817416818885</v>
+        <v>0.00177829682478012</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001719831827691337</v>
+        <v>0.002033097037237312</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00177962118019971</v>
+        <v>0.001749454355486838</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00177962118019971</v>
+        <v>0.001749454355486838</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001626888542556154</v>
+        <v>0.001907481235513428</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001755483019197808</v>
+        <v>0.001721823311680175</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001755483019197808</v>
+        <v>0.001721823311680175</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001536808212245975</v>
+        <v>0.001788075647782665</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001733441295303258</v>
+        <v>0.001696989356639992</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001733441295303258</v>
+        <v>0.001696989356639992</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001451963223299648</v>
+        <v>0.001675918526343563</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001714477230727661</v>
+        <v>0.001675827595037183</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001714477230727661</v>
+        <v>0.001675827595037183</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001372639840649897</v>
+        <v>0.001572213491052583</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001698950385469265</v>
+        <v>0.001658697752849194</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001698950385469265</v>
+        <v>0.001658697752849194</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001299509251722746</v>
+        <v>0.001476327786448533</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00168705284445172</v>
+        <v>0.001645773049436172</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00168705284445172</v>
+        <v>0.001645773049436172</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001232036142234813</v>
+        <v>0.001387667043749606</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.001679075556146523</v>
+        <v>0.001637319834609191</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001679075556146523</v>
+        <v>0.001637319834609191</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001170395583079489</v>
+        <v>0.001305665729517526</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001675558377720625</v>
+        <v>0.001633854208759213</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001675558377720625</v>
+        <v>0.001633854208759213</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001114278972267577</v>
+        <v>0.001229761999056764</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.001677168703476677</v>
+        <v>0.001636015835904902</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001677168703476677</v>
+        <v>0.001636015835904902</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001064439453895699</v>
+        <v>0.001161275311694898</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001684569001830066</v>
+        <v>0.001644437016859675</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001684569001830066</v>
+        <v>0.001644437016859675</v>
       </c>
       <c r="D20" t="n">
-        <v>0.001020204670830425</v>
+        <v>0.001101418074659404</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001698191149802363</v>
+        <v>0.001659496802628093</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001698191149802363</v>
+        <v>0.001659496802628093</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0009829643060358074</v>
+        <v>0.00104870115555465</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.001718683566237375</v>
+        <v>0.001681835516925827</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001718683566237375</v>
+        <v>0.001681835516925827</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0009516940460802934</v>
+        <v>0.001005169944076893</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.001746291270279645</v>
+        <v>0.001711662878893193</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001746291270279645</v>
+        <v>0.001711662878893193</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000926893357717999</v>
+        <v>0.0009697507550853341</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00178127584436477</v>
+        <v>0.001744894799599187</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00178127584436477</v>
+        <v>0.001744894799599187</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0009112861461971489</v>
+        <v>0.0009421070993555732</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.001818378241165034</v>
+        <v>0.00178898389237387</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001818378241165034</v>
+        <v>0.00178898389237387</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0009026616761666996</v>
+        <v>0.0009255687278579663</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.001867976015246634</v>
+        <v>0.00184168541743216</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001867976015246634</v>
+        <v>0.00184168541743216</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0009006740503230773</v>
+        <v>0.000918347542934297</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.001926368282530277</v>
+        <v>0.001903338190210399</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001926368282530277</v>
+        <v>0.001903338190210399</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0009084420976668168</v>
+        <v>0.0009280783817521023</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00199384292889806</v>
+        <v>0.001974289306158018</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00199384292889806</v>
+        <v>0.001974289306158018</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0009241303978777824</v>
+        <v>0.0009466453175923681</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.002070661602873533</v>
+        <v>0.002054760938374933</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002070661602873533</v>
+        <v>0.002054760938374933</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0009505964650006743</v>
+        <v>0.0009772384450227748</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.002156976725995875</v>
+        <v>0.002144891057686915</v>
       </c>
       <c r="C30" t="n">
-        <v>0.002156976725995875</v>
+        <v>0.002144891057686915</v>
       </c>
       <c r="D30" t="n">
-        <v>0.000985491857035038</v>
+        <v>0.001019083593752586</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.002252892750315151</v>
+        <v>0.002244759266350625</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002252892750315151</v>
+        <v>0.002244759266350625</v>
       </c>
       <c r="D31" t="n">
-        <v>0.001029415782901675</v>
+        <v>0.001071463135416891</v>
       </c>
     </row>
   </sheetData>
